--- a/testing/SPR-Epics-User-Stories-v2.xlsx
+++ b/testing/SPR-Epics-User-Stories-v2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="577">
   <si>
     <t>SPR TechForge — Epics &amp; User Stories v2.0 (2026-09-23)</t>
   </si>
@@ -157,7 +157,7 @@
     <t>Events — Administration</t>
   </si>
   <si>
-    <t>Event editor wizard, publish rules, event dashboard, registrants, check-in, recap, convert to candidate</t>
+    <t>Event editor wizard, publish rules, event dashboard, registrants, invite by email (Excel/CSV upload, editable invitation, outbox send), check-in, recap, convert to candidate</t>
   </si>
   <si>
     <t>MOD-27</t>
@@ -1166,6 +1166,57 @@
 • Given a published event with registrations, when I open the dashboard, then only Cancel and (master) Delete are offered
 • Given I cancel with a reason and notify, when I confirm, then registrants receive the cancellation email; the public page shows cancelled
 • Given I am a non-master admin, when I look for Delete permanently, then it is not offered</t>
+  </si>
+  <si>
+    <t>SPR-252</t>
+  </si>
+  <si>
+    <t>Invite by email: upload a contact list</t>
+  </si>
+  <si>
+    <t>Excel/CSV import with de-duplication (FR-27.13, FR-27.17).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Given an Excel file with Full Name, Email ID and Mobile Number columns (50 rows, 3 repeated), when I upload it on the Invite by email tab, then I see "47 added · 3 repeated in the file", the rows appear as Not sent yet and the counters update
+• Given the same file, when I upload it again, then the summary says 0 added and nothing is duplicated
+• Given a CSV without a header row and a row with only a mobile number, when I upload it, then emails and mobiles are still recognised; the mobile-only row shows "Mobile only" and is counted under Mobile only
+• Given a file whose rows have no email or mobile, when I upload it, then the summary says how many rows had no usable email or mobile and nothing is added
+• Given a list with people on it, when I search, filter by status, export CSV, remove one row and Clear list, then each works and the counters follow</t>
+  </si>
+  <si>
+    <t>SPR-253</t>
+  </si>
+  <si>
+    <t>Invite by email: edit, preview and test the invitation</t>
+  </si>
+  <si>
+    <t>Per-event wording with placeholders and a live preview (FR-27.14, FR-27.15).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Given the default wording, when I open the tab, then the preview shows banner, headline, message, facts box (when, where, speaker, free), the learning points, an orange button, closing line and an opt-out line
+• Given I change the subject and message using {{first_name}} and **bold**, when I look at the preview, then the placeholders are replaced with the first person's details and the bold text is bold
+• Given edited wording, when I click Save wording and reload the page, then the wording persists; Reset to default restores the built-in text
+• Given my address in "Send a test to yourself", when I click Send test, then I receive the email with a [TEST] subject within a couple of minutes and every link opens the event page with ?ref=email
+• Given the live site's event link pasted in "Registration link to use" (on QA), when I look at the preview and send a test, then the button and links use the live link with ?ref=email; a plain "sprtechforge.com" shows a red hint and is ignored</t>
+  </si>
+  <si>
+    <t>SPR-254</t>
+  </si>
+  <si>
+    <t>Invite by email: send to the list and track registrations</t>
+  </si>
+  <si>
+    <t>Outbox send with resumable statuses and attribution (FR-27.16, FR-27.17).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Given 5 people Not sent yet and 1 Mobile only, when I click Send invitation, then the button says 5 people, a confirmation appears, progress reaches 5/5 and the five rows become Invited with a time
+• Given one invited person registers through the emailed button, when I open the Overview tab, then Registrations by source shows email = 1 and that person's row shows Registered ✓
+• Given a send in progress, when I click Stop, then the remaining rows stay Not sent yet and the button offers them again
+• Given a row marked Failed, when I tick Include failed and send, then it is retried; with "Also resend" ticked, Invited rows are included and show ×2 afterwards
+• Given a draft (unpublished) event, when I try to send, then I am told to publish first and nothing is sent</t>
+  </si>
+  <si>
+    <t>SPR-253,SPR-282</t>
   </si>
   <si>
     <t>SPR-261</t>
@@ -2617,16 +2668,16 @@
         <v>48</v>
       </c>
       <c r="E9" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2816,16 +2867,16 @@
         <v>76</v>
       </c>
       <c r="E17" s="4">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F17" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H17" s="4">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -2840,7 +2891,7 @@
   <sheetPr>
     <tabColor rgb="FF059669"/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5179,28 +5230,28 @@
         <v>350</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>14</v>
+      <c r="F62" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G62" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>1</v>
@@ -5214,31 +5265,31 @@
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>14</v>
+      <c r="F63" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G63" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>1</v>
@@ -5252,37 +5303,37 @@
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>1</v>
@@ -5293,19 +5344,19 @@
         <v>363</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>15</v>
+        <v>367</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G65" s="2">
         <v>2</v>
@@ -5314,13 +5365,13 @@
         <v>93</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>1</v>
@@ -5328,22 +5379,22 @@
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>15</v>
+        <v>371</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G66" s="2">
         <v>2</v>
@@ -5352,13 +5403,13 @@
         <v>93</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>1</v>
@@ -5366,19 +5417,19 @@
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>14</v>
@@ -5396,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>1</v>
@@ -5407,7 +5458,7 @@
         <v>376</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>377</v>
@@ -5422,7 +5473,7 @@
         <v>15</v>
       </c>
       <c r="G68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>93</v>
@@ -5434,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>1</v>
@@ -5442,37 +5493,37 @@
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>1</v>
@@ -5480,37 +5531,37 @@
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="F70" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="2">
+        <v>2</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K70" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G70" s="2">
-        <v>1</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>1</v>
@@ -5521,7 +5572,7 @@
         <v>389</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>390</v>
@@ -5536,13 +5587,13 @@
         <v>15</v>
       </c>
       <c r="G71" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>1</v>
@@ -5551,30 +5602,30 @@
         <v>393</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>394</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>14</v>
+      <c r="F72" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>93</v>
@@ -5586,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>1</v>
@@ -5594,22 +5645,22 @@
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>14</v>
+      <c r="F73" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -5618,13 +5669,13 @@
         <v>93</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>1</v>
@@ -5632,40 +5683,40 @@
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>1</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5673,16 +5724,16 @@
         <v>408</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>14</v>
@@ -5700,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>1</v>
@@ -5708,22 +5759,22 @@
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>147</v>
+        <v>416</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -5732,13 +5783,13 @@
         <v>93</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>324</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>1</v>
@@ -5746,22 +5797,22 @@
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>111</v>
+        <v>420</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -5770,7 +5821,7 @@
         <v>93</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>1</v>
@@ -5784,10 +5835,10 @@
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>422</v>
@@ -5814,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>1</v>
@@ -5825,7 +5876,7 @@
         <v>425</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>426</v>
@@ -5836,23 +5887,23 @@
       <c r="E79" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>15</v>
+      <c r="F79" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>429</v>
+        <v>324</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>1</v>
@@ -5860,22 +5911,22 @@
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>14</v>
+      <c r="F80" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -5884,7 +5935,7 @@
         <v>93</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>1</v>
@@ -5898,10 +5949,10 @@
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>435</v>
@@ -5916,7 +5967,7 @@
         <v>14</v>
       </c>
       <c r="G81" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>93</v>
@@ -5928,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>1</v>
@@ -5939,7 +5990,7 @@
         <v>438</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>439</v>
@@ -5960,7 +6011,7 @@
         <v>93</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>1</v>
@@ -5977,7 +6028,7 @@
         <v>443</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>444</v>
@@ -5988,8 +6039,8 @@
       <c r="E83" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>15</v>
+      <c r="F83" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -6004,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>1</v>
@@ -6015,7 +6066,7 @@
         <v>447</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>448</v>
@@ -6026,8 +6077,8 @@
       <c r="E84" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="F84" s="9" t="s">
-        <v>147</v>
+      <c r="F84" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -6036,13 +6087,13 @@
         <v>93</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>451</v>
+        <v>209</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>1</v>
@@ -6050,10 +6101,10 @@
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>452</v>
@@ -6074,13 +6125,13 @@
         <v>93</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>1</v>
+        <v>455</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>1</v>
@@ -6088,25 +6139,25 @@
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>93</v>
@@ -6118,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>1</v>
@@ -6126,22 +6177,22 @@
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>15</v>
+        <v>463</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -6150,13 +6201,13 @@
         <v>93</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>1</v>
+        <v>464</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>1</v>
@@ -6164,31 +6215,31 @@
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>147</v>
+        <v>467</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G88" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>1</v>
@@ -6202,25 +6253,25 @@
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>393</v>
+        <v>455</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>14</v>
+        <v>470</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>93</v>
@@ -6240,25 +6291,25 @@
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>14</v>
+        <v>473</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G90" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>93</v>
@@ -6270,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>393</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>1</v>
@@ -6278,19 +6329,19 @@
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>147</v>
@@ -6308,7 +6359,7 @@
         <v>1</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>469</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>1</v>
@@ -6316,22 +6367,22 @@
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>477</v>
+        <v>406</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>147</v>
+        <v>481</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -6340,13 +6391,13 @@
         <v>93</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>363</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>1</v>
@@ -6354,37 +6405,37 @@
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>111</v>
+        <v>485</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G93" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>1</v>
@@ -6392,10 +6443,10 @@
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>487</v>
@@ -6406,23 +6457,23 @@
       <c r="E94" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>15</v>
+      <c r="F94" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G94" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>1</v>
+        <v>482</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>1</v>
@@ -6433,7 +6484,7 @@
         <v>490</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>491</v>
@@ -6444,23 +6495,23 @@
       <c r="E95" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="F95" s="7" t="s">
-        <v>15</v>
+      <c r="F95" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G95" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>494</v>
+        <v>376</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>1</v>
@@ -6468,25 +6519,25 @@
     </row>
     <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>15</v>
+      <c r="F96" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>93</v>
@@ -6498,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>485</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>1</v>
@@ -6506,10 +6557,10 @@
     </row>
     <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>500</v>
@@ -6520,11 +6571,11 @@
       <c r="E97" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>147</v>
+      <c r="F97" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>93</v>
@@ -6536,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>495</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>1</v>
@@ -6547,7 +6598,7 @@
         <v>503</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>504</v>
@@ -6558,23 +6609,23 @@
       <c r="E98" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F98" s="8" t="s">
-        <v>111</v>
+      <c r="F98" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G98" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>1</v>
@@ -6582,37 +6633,37 @@
     </row>
     <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>111</v>
+        <v>511</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>1</v>
+        <v>498</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>1</v>
@@ -6620,10 +6671,10 @@
     </row>
     <row r="100" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>513</v>
@@ -6650,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>1</v>
+        <v>508</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>1</v>
@@ -6661,7 +6712,7 @@
         <v>516</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>517</v>
@@ -6682,13 +6733,13 @@
         <v>93</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>1</v>
+        <v>498</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>1</v>
@@ -6699,7 +6750,7 @@
         <v>520</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>521</v>
@@ -6720,7 +6771,7 @@
         <v>93</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>1</v>
@@ -6729,15 +6780,15 @@
         <v>1</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>524</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>526</v>
@@ -6758,45 +6809,45 @@
         <v>93</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>297</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>529</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>15</v>
+      <c r="F104" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>1</v>
@@ -6810,78 +6861,78 @@
     </row>
     <row r="105" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="F105" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G105" s="2">
+        <v>1</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G105" s="2">
-        <v>1</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="E106" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="F106" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G106" s="2">
+        <v>1</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L106" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G106" s="2">
-        <v>3</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6889,16 +6940,16 @@
         <v>543</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>15</v>
@@ -6910,7 +6961,7 @@
         <v>93</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>1</v>
@@ -6924,22 +6975,22 @@
     </row>
     <row r="108" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>15</v>
+        <v>551</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -6948,7 +6999,7 @@
         <v>93</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>1</v>
@@ -6962,25 +7013,25 @@
     </row>
     <row r="109" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>111</v>
+        <v>555</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G109" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>93</v>
@@ -6992,28 +7043,142 @@
         <v>1</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="L109" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G110" s="2">
+        <v>2</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" s="2">
+        <v>1</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <dataValidations count="5">
-    <dataValidation type="list" sqref="F2:F109">
+    <dataValidation type="list" sqref="F2:F112">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G2:G109">
+    <dataValidation type="list" sqref="G2:G112">
       <formula1>"1,2,3,5,8"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H109">
+    <dataValidation type="list" sqref="H2:H112">
       <formula1>"Backlog,Sprint,In Design,In Test,Blocked,Failed,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I109">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I112">
       <formula1>"S1,S2,S3,S4,S5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J109">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J112">
       <formula1>"Tester 1,Tester 2,Tester 3,Tester 4,Lead"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7027,7 +7192,7 @@
   <sheetPr>
     <tabColor rgb="FF0891B2"/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7045,7 +7210,7 @@
         <v>84</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>77</v>
@@ -7063,10 +7228,10 @@
         <v>82</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7074,7 +7239,7 @@
         <v>94</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>88</v>
@@ -7092,10 +7257,10 @@
         <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7103,7 +7268,7 @@
         <v>94</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>95</v>
@@ -7121,10 +7286,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7132,7 +7297,7 @@
         <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>99</v>
@@ -7150,10 +7315,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7161,7 +7326,7 @@
         <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>118</v>
@@ -7179,10 +7344,10 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7190,7 +7355,7 @@
         <v>94</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>126</v>
@@ -7208,10 +7373,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7219,7 +7384,7 @@
         <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>135</v>
@@ -7237,10 +7402,10 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7248,7 +7413,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>165</v>
@@ -7266,10 +7431,10 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7277,7 +7442,7 @@
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>200</v>
@@ -7295,10 +7460,10 @@
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7306,7 +7471,7 @@
         <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -7324,10 +7489,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7335,7 +7500,7 @@
         <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>316</v>
@@ -7353,10 +7518,10 @@
         <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7364,16 +7529,16 @@
         <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>14</v>
@@ -7382,10 +7547,10 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7393,16 +7558,16 @@
         <v>94</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>14</v>
@@ -7411,10 +7576,10 @@
         <v>2</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7422,16 +7587,16 @@
         <v>94</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>14</v>
@@ -7440,10 +7605,10 @@
         <v>2</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7451,16 +7616,16 @@
         <v>94</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>14</v>
@@ -7469,10 +7634,10 @@
         <v>2</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7480,16 +7645,16 @@
         <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>14</v>
@@ -7498,10 +7663,10 @@
         <v>2</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7509,16 +7674,16 @@
         <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>14</v>
@@ -7527,10 +7692,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7538,16 +7703,16 @@
         <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>14</v>
@@ -7556,10 +7721,10 @@
         <v>2</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7567,16 +7732,16 @@
         <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>14</v>
@@ -7585,10 +7750,10 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7596,16 +7761,16 @@
         <v>94</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>14</v>
@@ -7614,10 +7779,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7625,16 +7790,16 @@
         <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>14</v>
@@ -7643,10 +7808,10 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7654,16 +7819,16 @@
         <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>14</v>
@@ -7672,10 +7837,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7683,16 +7848,16 @@
         <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>14</v>
@@ -7701,10 +7866,10 @@
         <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7712,7 +7877,7 @@
         <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>103</v>
@@ -7730,10 +7895,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7741,7 +7906,7 @@
         <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>114</v>
@@ -7759,10 +7924,10 @@
         <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7770,7 +7935,7 @@
         <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>170</v>
@@ -7788,10 +7953,10 @@
         <v>2</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7799,7 +7964,7 @@
         <v>94</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>209</v>
@@ -7817,10 +7982,10 @@
         <v>2</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7828,7 +7993,7 @@
         <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>308</v>
@@ -7846,10 +8011,10 @@
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7857,16 +8022,16 @@
         <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>15</v>
@@ -7875,10 +8040,10 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7886,16 +8051,16 @@
         <v>94</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>15</v>
@@ -7904,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7915,16 +8080,16 @@
         <v>94</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>15</v>
@@ -7933,10 +8098,10 @@
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7944,16 +8109,16 @@
         <v>94</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>15</v>
@@ -7962,10 +8127,10 @@
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7973,16 +8138,16 @@
         <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>15</v>
@@ -7991,10 +8156,10 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8002,16 +8167,16 @@
         <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>15</v>
@@ -8020,10 +8185,10 @@
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8031,16 +8196,16 @@
         <v>94</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>15</v>
@@ -8049,10 +8214,10 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8060,7 +8225,7 @@
         <v>112</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>191</v>
@@ -8078,10 +8243,10 @@
         <v>2</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8089,7 +8254,7 @@
         <v>112</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>222</v>
@@ -8107,10 +8272,10 @@
         <v>2</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8118,7 +8283,7 @@
         <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>234</v>
@@ -8136,10 +8301,10 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8147,7 +8312,7 @@
         <v>112</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>312</v>
@@ -8165,10 +8330,10 @@
         <v>3</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8176,7 +8341,7 @@
         <v>112</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>346</v>
@@ -8194,10 +8359,10 @@
         <v>2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8205,16 +8370,16 @@
         <v>112</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>539</v>
+        <v>358</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>540</v>
+        <v>359</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>531</v>
+        <v>304</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>14</v>
@@ -8223,10 +8388,10 @@
         <v>3</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8234,28 +8399,28 @@
         <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>122</v>
+        <v>552</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>123</v>
+        <v>553</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>15</v>
+        <v>544</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8263,28 +8428,28 @@
         <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8292,13 +8457,13 @@
         <v>112</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>127</v>
@@ -8310,10 +8475,10 @@
         <v>2</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8321,13 +8486,13 @@
         <v>112</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>127</v>
@@ -8336,13 +8501,13 @@
         <v>15</v>
       </c>
       <c r="G45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8350,16 +8515,16 @@
         <v>112</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>15</v>
@@ -8368,10 +8533,10 @@
         <v>1</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8379,13 +8544,13 @@
         <v>112</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>166</v>
@@ -8394,13 +8559,13 @@
         <v>15</v>
       </c>
       <c r="G47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8408,13 +8573,13 @@
         <v>112</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>166</v>
@@ -8426,10 +8591,10 @@
         <v>2</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8437,13 +8602,13 @@
         <v>112</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>166</v>
@@ -8455,10 +8620,10 @@
         <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8466,16 +8631,16 @@
         <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>15</v>
@@ -8484,10 +8649,10 @@
         <v>2</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8495,16 +8660,16 @@
         <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>15</v>
@@ -8513,10 +8678,10 @@
         <v>2</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8524,13 +8689,13 @@
         <v>112</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>218</v>
@@ -8542,10 +8707,10 @@
         <v>2</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8553,16 +8718,16 @@
         <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>15</v>
@@ -8571,10 +8736,10 @@
         <v>2</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8582,13 +8747,13 @@
         <v>112</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>235</v>
@@ -8600,10 +8765,10 @@
         <v>2</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8611,13 +8776,13 @@
         <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>235</v>
@@ -8629,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8640,13 +8805,13 @@
         <v>112</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>235</v>
@@ -8658,10 +8823,10 @@
         <v>2</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8669,16 +8834,16 @@
         <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>15</v>
@@ -8687,10 +8852,10 @@
         <v>2</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8698,13 +8863,13 @@
         <v>112</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>304</v>
@@ -8716,10 +8881,10 @@
         <v>2</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8727,13 +8892,13 @@
         <v>112</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>304</v>
@@ -8745,10 +8910,10 @@
         <v>2</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8756,13 +8921,13 @@
         <v>112</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>304</v>
@@ -8774,10 +8939,10 @@
         <v>2</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8785,16 +8950,16 @@
         <v>112</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>15</v>
@@ -8803,10 +8968,10 @@
         <v>2</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8814,28 +8979,28 @@
         <v>112</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8843,28 +9008,28 @@
         <v>112</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G63" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8872,16 +9037,16 @@
         <v>112</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>438</v>
+        <v>376</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>15</v>
@@ -8890,10 +9055,10 @@
         <v>2</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8901,16 +9066,16 @@
         <v>112</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>530</v>
+        <v>380</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>532</v>
+        <v>381</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>15</v>
@@ -8919,10 +9084,10 @@
         <v>2</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8930,16 +9095,16 @@
         <v>112</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>547</v>
+        <v>389</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>548</v>
+        <v>390</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>15</v>
@@ -8948,10 +9113,10 @@
         <v>1</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8959,28 +9124,28 @@
         <v>112</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>143</v>
+        <v>451</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>144</v>
+        <v>452</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>147</v>
+        <v>434</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G67" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8988,28 +9153,28 @@
         <v>112</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>148</v>
+        <v>543</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>149</v>
+        <v>545</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>147</v>
+        <v>544</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G68" s="2">
         <v>2</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9017,28 +9182,28 @@
         <v>112</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="D69" s="2" t="s">
-        <v>153</v>
+        <v>561</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>147</v>
+        <v>544</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9046,16 +9211,16 @@
         <v>112</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>385</v>
+        <v>143</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>386</v>
+        <v>144</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>351</v>
+        <v>127</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>147</v>
@@ -9064,10 +9229,10 @@
         <v>1</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9075,28 +9240,28 @@
         <v>112</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>412</v>
+        <v>148</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>413</v>
+        <v>149</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>396</v>
+        <v>127</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G71" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9104,16 +9269,16 @@
         <v>112</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>447</v>
+        <v>152</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>448</v>
+        <v>153</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>421</v>
+        <v>127</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>147</v>
@@ -9122,10 +9287,10 @@
         <v>1</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9133,16 +9298,16 @@
         <v>112</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>461</v>
+        <v>398</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>462</v>
+        <v>399</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>421</v>
+        <v>364</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>147</v>
@@ -9151,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9162,16 +9327,16 @@
         <v>112</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>473</v>
+        <v>425</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>474</v>
+        <v>426</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>465</v>
+        <v>409</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>147</v>
@@ -9180,10 +9345,10 @@
         <v>1</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="75" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9191,16 +9356,16 @@
         <v>112</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>147</v>
@@ -9209,10 +9374,10 @@
         <v>1</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9220,28 +9385,28 @@
         <v>112</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>107</v>
+        <v>474</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>108</v>
+        <v>475</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>111</v>
+        <v>434</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="77" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9249,115 +9414,115 @@
         <v>112</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>551</v>
+        <v>486</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>552</v>
+        <v>487</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>111</v>
+        <v>478</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>272</v>
+        <v>490</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>274</v>
+        <v>491</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>14</v>
+        <v>478</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="79" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>14</v>
+        <v>89</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G79" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="80" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>281</v>
+        <v>564</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>282</v>
+        <v>565</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>15</v>
+        <v>544</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9365,28 +9530,28 @@
         <v>164</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>15</v>
+      <c r="F81" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G81" s="2">
         <v>2</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="82" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9394,28 +9559,28 @@
         <v>164</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>342</v>
+        <v>278</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>15</v>
+        <v>273</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9423,28 +9588,28 @@
         <v>164</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>389</v>
+        <v>281</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>390</v>
+        <v>282</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>351</v>
+        <v>273</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9452,16 +9617,16 @@
         <v>164</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>485</v>
+        <v>285</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>487</v>
+        <v>286</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>486</v>
+        <v>273</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>15</v>
@@ -9470,10 +9635,10 @@
         <v>2</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="85" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9481,16 +9646,16 @@
         <v>164</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>490</v>
+        <v>341</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>491</v>
+        <v>342</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>486</v>
+        <v>304</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>15</v>
@@ -9499,10 +9664,10 @@
         <v>2</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="86" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9510,28 +9675,28 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>495</v>
+        <v>402</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>496</v>
+        <v>403</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>486</v>
+        <v>364</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9539,16 +9704,16 @@
         <v>164</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>543</v>
+        <v>498</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>15</v>
@@ -9557,10 +9722,10 @@
         <v>2</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9568,28 +9733,28 @@
         <v>164</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>226</v>
+        <v>503</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>227</v>
+        <v>504</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>147</v>
+        <v>499</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G88" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9597,28 +9762,28 @@
         <v>164</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>247</v>
+        <v>508</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>248</v>
+        <v>509</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>147</v>
+        <v>499</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9626,28 +9791,28 @@
         <v>164</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>263</v>
+        <v>556</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>264</v>
+        <v>557</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>147</v>
+        <v>544</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G90" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9655,28 +9820,28 @@
         <v>164</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>337</v>
+        <v>226</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>304</v>
+        <v>218</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G91" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="92" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9684,16 +9849,16 @@
         <v>164</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>499</v>
+        <v>247</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>486</v>
+        <v>235</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>147</v>
@@ -9702,10 +9867,10 @@
         <v>1</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="93" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9713,28 +9878,28 @@
         <v>164</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>511</v>
+        <v>263</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>513</v>
+        <v>264</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>512</v>
+        <v>235</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G93" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="94" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9742,28 +9907,28 @@
         <v>164</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>535</v>
+        <v>337</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>536</v>
+        <v>338</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>531</v>
+        <v>304</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G94" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="95" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9771,28 +9936,28 @@
         <v>164</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>160</v>
+        <v>512</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>161</v>
+        <v>513</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>111</v>
+        <v>499</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G95" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="96" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9800,28 +9965,28 @@
         <v>164</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>196</v>
+        <v>524</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>197</v>
+        <v>526</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>111</v>
+        <v>525</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9829,28 +9994,28 @@
         <v>164</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>213</v>
+        <v>548</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>214</v>
+        <v>549</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>111</v>
+        <v>544</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9858,28 +10023,28 @@
         <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>252</v>
+        <v>161</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>235</v>
+        <v>127</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G98" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9887,16 +10052,16 @@
         <v>164</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>416</v>
+        <v>196</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>417</v>
+        <v>197</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>396</v>
+        <v>166</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>111</v>
@@ -9905,10 +10070,10 @@
         <v>1</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9916,16 +10081,16 @@
         <v>164</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>481</v>
+        <v>213</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>482</v>
+        <v>214</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>465</v>
+        <v>201</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>111</v>
@@ -9934,10 +10099,10 @@
         <v>1</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9945,16 +10110,16 @@
         <v>164</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>516</v>
+        <v>251</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>517</v>
+        <v>252</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>512</v>
+        <v>235</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>111</v>
@@ -9963,97 +10128,97 @@
         <v>1</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>289</v>
+        <v>429</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>15</v>
+        <v>409</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G102" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>293</v>
+        <v>494</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>294</v>
+        <v>495</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>147</v>
+        <v>478</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>267</v>
+        <v>529</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>268</v>
+        <v>530</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>235</v>
+        <v>525</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10061,28 +10226,28 @@
         <v>271</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>503</v>
+        <v>289</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>504</v>
+        <v>290</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>111</v>
+        <v>273</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G105" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10090,94 +10255,94 @@
         <v>271</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>507</v>
+        <v>293</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>508</v>
+        <v>294</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>111</v>
+        <v>273</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G106" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>525</v>
+        <v>267</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>526</v>
+        <v>268</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>147</v>
+        <v>235</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G107" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>297</v>
+        <v>516</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>298</v>
+        <v>517</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>273</v>
+        <v>499</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>520</v>
@@ -10186,7 +10351,7 @@
         <v>521</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>111</v>
@@ -10195,19 +10360,106 @@
         <v>1</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G110" s="2">
+        <v>1</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G111" s="2">
+        <v>2</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>572</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="H2:H109">
+    <dataValidation type="list" sqref="H2:H112">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I109">
+    <dataValidation type="list" sqref="I2:I112">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/testing/SPR-Epics-User-Stories-v2.xlsx
+++ b/testing/SPR-Epics-User-Stories-v2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="582">
   <si>
     <t>SPR TechForge — Epics &amp; User Stories v2.0 (2026-09-23)</t>
   </si>
@@ -1217,6 +1217,25 @@
   </si>
   <si>
     <t>SPR-253,SPR-282</t>
+  </si>
+  <si>
+    <t>SPR-255</t>
+  </si>
+  <si>
+    <t>Post-event follow-up survey</t>
+  </si>
+  <si>
+    <t>Follow-up email with Yes/No buttons, public survey page with two branches, Feedback tab (FR-27.18–20, FR-28.17, BR-27.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Given a completed event and a list of registrants uploaded on the Invite tab, when I switch "What to send" to Follow-up survey, set the Next session label and send a test to myself, then the mail asks "Did you join the live session?" with a Yes and a No button; each opens the survey page with that answer and my email pre-filled; the next session text appears in the mail
+• Given the survey page opened from the No button, when I pick "link did not work on my phone", next session Yes, recording Yes, course Maybe, mode Online, time Evening and submit, then a thank-you card confirms the next session details and the recording; the Feedback tab shows my row once with the reason, and the "Why people did not join" bar updates
+• Given the same email opens the page again and answers Yes with 4 stars, when I submit, then the earlier row is updated, not duplicated; Avg rating and Joined counters update
+• Given the page with no answer chosen or an invalid email, when I try to submit, then I am blocked with a clear message and nothing is saved
+• Given answers on the Feedback tab, when I filter Interested in course, click Copy emails, and Export CSV, then the filter keeps only yes/maybe rows, the clipboard holds their emails, and the CSV contains reason, next session, course interest and comments</t>
+  </si>
+  <si>
+    <t>SPR-252,SPR-254</t>
   </si>
   <si>
     <t>SPR-261</t>
@@ -2668,16 +2687,16 @@
         <v>48</v>
       </c>
       <c r="E9" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2867,16 +2886,16 @@
         <v>76</v>
       </c>
       <c r="E17" s="4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F17" s="4">
         <v>31</v>
       </c>
       <c r="G17" s="4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H17" s="4">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2891,7 +2910,7 @@
   <sheetPr>
     <tabColor rgb="FF059669"/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5344,34 +5363,34 @@
         <v>363</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" s="2">
+        <v>3</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G65" s="2">
-        <v>2</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>1</v>
@@ -5382,16 +5401,16 @@
         <v>368</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>14</v>
@@ -5409,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>363</v>
+        <v>316</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>1</v>
@@ -5417,19 +5436,19 @@
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>14</v>
@@ -5455,22 +5474,22 @@
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>15</v>
+        <v>380</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G68" s="2">
         <v>2</v>
@@ -5479,13 +5498,13 @@
         <v>93</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>1</v>
@@ -5493,19 +5512,19 @@
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>15</v>
@@ -5523,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>312</v>
+        <v>377</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>1</v>
@@ -5531,22 +5550,22 @@
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>14</v>
+        <v>388</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G70" s="2">
         <v>2</v>
@@ -5555,13 +5574,13 @@
         <v>93</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>388</v>
+        <v>312</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>1</v>
@@ -5572,7 +5591,7 @@
         <v>389</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>390</v>
@@ -5583,17 +5602,17 @@
       <c r="E71" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>15</v>
+      <c r="F71" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G71" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>1</v>
@@ -5610,7 +5629,7 @@
         <v>394</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>395</v>
@@ -5631,13 +5650,13 @@
         <v>93</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>1</v>
+        <v>398</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>1</v>
@@ -5645,22 +5664,22 @@
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>147</v>
+        <v>402</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -5669,13 +5688,13 @@
         <v>93</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>372</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>1</v>
@@ -5683,78 +5702,78 @@
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>15</v>
+        <v>406</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G74" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>407</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="F75" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="2">
+        <v>3</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K75" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="L75" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G75" s="2">
-        <v>2</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5762,22 +5781,22 @@
         <v>413</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G76" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>93</v>
@@ -5789,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>1</v>
@@ -5797,22 +5816,22 @@
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>15</v>
+        <v>421</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -5835,25 +5854,25 @@
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>14</v>
+        <v>425</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>93</v>
@@ -5865,7 +5884,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>372</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>1</v>
@@ -5873,37 +5892,37 @@
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>147</v>
+        <v>429</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>324</v>
+        <v>377</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>1</v>
@@ -5911,22 +5930,22 @@
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>111</v>
+        <v>433</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -5935,13 +5954,13 @@
         <v>93</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>1</v>
@@ -5949,10 +5968,10 @@
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>435</v>
@@ -5963,17 +5982,17 @@
       <c r="E81" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="F81" s="6" t="s">
-        <v>14</v>
+      <c r="F81" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>1</v>
@@ -5990,19 +6009,19 @@
         <v>438</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>15</v>
+        <v>442</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G82" s="2">
         <v>2</v>
@@ -6017,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>442</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>1</v>
@@ -6028,7 +6047,7 @@
         <v>443</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>444</v>
@@ -6039,11 +6058,11 @@
       <c r="E83" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F83" s="6" t="s">
-        <v>14</v>
+      <c r="F83" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G83" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>93</v>
@@ -6055,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>1</v>
+        <v>447</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>1</v>
@@ -6063,19 +6082,19 @@
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>14</v>
@@ -6093,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>1</v>
@@ -6101,37 +6120,37 @@
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>15</v>
+        <v>455</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G85" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>455</v>
+        <v>209</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>1</v>
@@ -6142,7 +6161,7 @@
         <v>456</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>457</v>
@@ -6157,19 +6176,19 @@
         <v>15</v>
       </c>
       <c r="G86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>316</v>
+        <v>460</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>1</v>
@@ -6177,22 +6196,22 @@
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>147</v>
+        <v>464</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -6201,13 +6220,13 @@
         <v>93</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>464</v>
+        <v>316</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>1</v>
@@ -6215,37 +6234,37 @@
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>15</v>
+        <v>468</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>1</v>
@@ -6253,19 +6272,19 @@
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>15</v>
@@ -6291,25 +6310,25 @@
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G90" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>93</v>
@@ -6329,22 +6348,22 @@
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>147</v>
+        <v>478</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -6353,7 +6372,7 @@
         <v>93</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>1</v>
@@ -6367,22 +6386,22 @@
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>406</v>
+        <v>479</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>478</v>
+        <v>439</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>14</v>
+        <v>482</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -6391,7 +6410,7 @@
         <v>93</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>1</v>
@@ -6405,25 +6424,25 @@
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>482</v>
+        <v>411</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>93</v>
@@ -6435,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>406</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>1</v>
@@ -6443,37 +6462,37 @@
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>147</v>
+        <v>490</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G94" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>482</v>
+        <v>411</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>1</v>
@@ -6481,19 +6500,19 @@
     </row>
     <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>147</v>
@@ -6511,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>376</v>
+        <v>487</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>1</v>
@@ -6519,22 +6538,22 @@
     </row>
     <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>111</v>
+        <v>498</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -6543,13 +6562,13 @@
         <v>93</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>1</v>
@@ -6557,10 +6576,10 @@
     </row>
     <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>500</v>
@@ -6571,11 +6590,11 @@
       <c r="E97" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>15</v>
+      <c r="F97" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>93</v>
@@ -6598,16 +6617,16 @@
         <v>503</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>15</v>
@@ -6625,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>507</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>1</v>
@@ -6636,7 +6655,7 @@
         <v>508</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>509</v>
@@ -6663,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>1</v>
@@ -6671,25 +6690,25 @@
     </row>
     <row r="100" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>147</v>
+        <v>516</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G100" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>93</v>
@@ -6701,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>1</v>
@@ -6709,22 +6728,22 @@
     </row>
     <row r="101" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>111</v>
+        <v>520</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -6733,13 +6752,13 @@
         <v>93</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>1</v>
@@ -6747,19 +6766,19 @@
     </row>
     <row r="102" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>111</v>
@@ -6777,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>1</v>
+        <v>503</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>1</v>
@@ -6785,10 +6804,10 @@
     </row>
     <row r="103" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>526</v>
@@ -6799,8 +6818,8 @@
       <c r="E103" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>147</v>
+      <c r="F103" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -6809,7 +6828,7 @@
         <v>93</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>1</v>
@@ -6826,19 +6845,19 @@
         <v>529</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>111</v>
+        <v>533</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -6861,19 +6880,19 @@
     </row>
     <row r="105" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>111</v>
@@ -6885,7 +6904,7 @@
         <v>93</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>1</v>
@@ -6894,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>537</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6902,7 +6921,7 @@
         <v>538</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>539</v>
@@ -6913,8 +6932,8 @@
       <c r="E106" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F106" s="9" t="s">
-        <v>147</v>
+      <c r="F106" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -6929,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>297</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>542</v>
@@ -6940,37 +6959,37 @@
         <v>543</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="F107" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="L107" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G107" s="2">
-        <v>2</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6978,28 +6997,28 @@
         <v>548</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>147</v>
+        <v>552</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>1</v>
@@ -7013,37 +7032,37 @@
     </row>
     <row r="109" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>14</v>
+        <v>556</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G109" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>1</v>
@@ -7051,37 +7070,37 @@
     </row>
     <row r="110" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>15</v>
+        <v>560</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G110" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>1</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>1</v>
@@ -7089,31 +7108,31 @@
     </row>
     <row r="111" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G111" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>1</v>
@@ -7127,22 +7146,22 @@
     </row>
     <row r="112" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>111</v>
+        <v>568</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -7160,25 +7179,63 @@
         <v>1</v>
       </c>
       <c r="L112" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <dataValidations count="5">
-    <dataValidation type="list" sqref="F2:F112">
+    <dataValidation type="list" sqref="F2:F113">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G2:G112">
+    <dataValidation type="list" sqref="G2:G113">
       <formula1>"1,2,3,5,8"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H112">
+    <dataValidation type="list" sqref="H2:H113">
       <formula1>"Backlog,Sprint,In Design,In Test,Blocked,Failed,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I112">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I113">
       <formula1>"S1,S2,S3,S4,S5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J112">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J113">
       <formula1>"Tester 1,Tester 2,Tester 3,Tester 4,Lead"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7192,7 +7249,7 @@
   <sheetPr>
     <tabColor rgb="FF0891B2"/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7210,7 +7267,7 @@
         <v>84</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>77</v>
@@ -7228,10 +7285,10 @@
         <v>82</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7239,7 +7296,7 @@
         <v>94</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>88</v>
@@ -7257,10 +7314,10 @@
         <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7268,7 +7325,7 @@
         <v>94</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>95</v>
@@ -7286,10 +7343,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7297,7 +7354,7 @@
         <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>99</v>
@@ -7315,10 +7372,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7326,7 +7383,7 @@
         <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>118</v>
@@ -7344,10 +7401,10 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7355,7 +7412,7 @@
         <v>94</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>126</v>
@@ -7373,10 +7430,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7384,7 +7441,7 @@
         <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>135</v>
@@ -7402,10 +7459,10 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7413,7 +7470,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>165</v>
@@ -7431,10 +7488,10 @@
         <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7442,7 +7499,7 @@
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>200</v>
@@ -7460,10 +7517,10 @@
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7471,7 +7528,7 @@
         <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>303</v>
@@ -7489,10 +7546,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7500,7 +7557,7 @@
         <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>316</v>
@@ -7518,10 +7575,10 @@
         <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7529,16 +7586,16 @@
         <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>14</v>
@@ -7547,10 +7604,10 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7558,16 +7615,16 @@
         <v>94</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>14</v>
@@ -7576,10 +7633,10 @@
         <v>2</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7587,16 +7644,16 @@
         <v>94</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>14</v>
@@ -7605,10 +7662,10 @@
         <v>2</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7616,16 +7673,16 @@
         <v>94</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>14</v>
@@ -7634,10 +7691,10 @@
         <v>2</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7645,16 +7702,16 @@
         <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>14</v>
@@ -7663,10 +7720,10 @@
         <v>2</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7674,16 +7731,16 @@
         <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>14</v>
@@ -7692,10 +7749,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7703,16 +7760,16 @@
         <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>14</v>
@@ -7721,10 +7778,10 @@
         <v>2</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7732,16 +7789,16 @@
         <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>14</v>
@@ -7750,10 +7807,10 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7761,16 +7818,16 @@
         <v>94</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>14</v>
@@ -7779,10 +7836,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7790,16 +7847,16 @@
         <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>14</v>
@@ -7808,10 +7865,10 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7819,16 +7876,16 @@
         <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>14</v>
@@ -7837,10 +7894,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7848,16 +7905,16 @@
         <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>14</v>
@@ -7866,10 +7923,10 @@
         <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7877,7 +7934,7 @@
         <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>103</v>
@@ -7895,10 +7952,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7906,7 +7963,7 @@
         <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>114</v>
@@ -7924,10 +7981,10 @@
         <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7935,7 +7992,7 @@
         <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>170</v>
@@ -7953,10 +8010,10 @@
         <v>2</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7964,7 +8021,7 @@
         <v>94</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>209</v>
@@ -7982,10 +8039,10 @@
         <v>2</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7993,7 +8050,7 @@
         <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>308</v>
@@ -8011,10 +8068,10 @@
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8022,16 +8079,16 @@
         <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>15</v>
@@ -8040,10 +8097,10 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8051,16 +8108,16 @@
         <v>94</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>15</v>
@@ -8069,10 +8126,10 @@
         <v>1</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8080,16 +8137,16 @@
         <v>94</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>15</v>
@@ -8098,10 +8155,10 @@
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8109,16 +8166,16 @@
         <v>94</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>15</v>
@@ -8127,10 +8184,10 @@
         <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8138,16 +8195,16 @@
         <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>15</v>
@@ -8156,10 +8213,10 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8167,16 +8224,16 @@
         <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>15</v>
@@ -8185,10 +8242,10 @@
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8196,16 +8253,16 @@
         <v>94</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>15</v>
@@ -8214,10 +8271,10 @@
         <v>1</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8225,7 +8282,7 @@
         <v>112</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>191</v>
@@ -8243,10 +8300,10 @@
         <v>2</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8254,7 +8311,7 @@
         <v>112</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>222</v>
@@ -8272,10 +8329,10 @@
         <v>2</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8283,7 +8340,7 @@
         <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>234</v>
@@ -8301,10 +8358,10 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8312,7 +8369,7 @@
         <v>112</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>312</v>
@@ -8330,10 +8387,10 @@
         <v>3</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8341,7 +8398,7 @@
         <v>112</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>346</v>
@@ -8359,10 +8416,10 @@
         <v>2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8370,7 +8427,7 @@
         <v>112</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>358</v>
@@ -8388,10 +8445,10 @@
         <v>3</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8399,16 +8456,16 @@
         <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>14</v>
@@ -8417,10 +8474,10 @@
         <v>3</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8428,7 +8485,7 @@
         <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>122</v>
@@ -8446,10 +8503,10 @@
         <v>1</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8457,7 +8514,7 @@
         <v>112</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>131</v>
@@ -8475,10 +8532,10 @@
         <v>2</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8486,7 +8543,7 @@
         <v>112</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>139</v>
@@ -8504,10 +8561,10 @@
         <v>2</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8515,7 +8572,7 @@
         <v>112</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>156</v>
@@ -8533,10 +8590,10 @@
         <v>1</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8544,7 +8601,7 @@
         <v>112</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>174</v>
@@ -8562,10 +8619,10 @@
         <v>1</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8573,7 +8630,7 @@
         <v>112</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>178</v>
@@ -8591,10 +8648,10 @@
         <v>2</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8602,7 +8659,7 @@
         <v>112</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>183</v>
@@ -8620,10 +8677,10 @@
         <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8631,7 +8688,7 @@
         <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>187</v>
@@ -8649,10 +8706,10 @@
         <v>2</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8660,7 +8717,7 @@
         <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>205</v>
@@ -8678,10 +8735,10 @@
         <v>2</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8689,7 +8746,7 @@
         <v>112</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>217</v>
@@ -8707,10 +8764,10 @@
         <v>2</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8718,7 +8775,7 @@
         <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>230</v>
@@ -8736,10 +8793,10 @@
         <v>2</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8747,7 +8804,7 @@
         <v>112</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>239</v>
@@ -8765,10 +8822,10 @@
         <v>2</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8776,7 +8833,7 @@
         <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>243</v>
@@ -8794,10 +8851,10 @@
         <v>2</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8805,7 +8862,7 @@
         <v>112</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>255</v>
@@ -8823,10 +8880,10 @@
         <v>2</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8834,7 +8891,7 @@
         <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>259</v>
@@ -8852,10 +8909,10 @@
         <v>2</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8863,7 +8920,7 @@
         <v>112</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>320</v>
@@ -8881,10 +8938,10 @@
         <v>2</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8892,7 +8949,7 @@
         <v>112</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>324</v>
@@ -8910,10 +8967,10 @@
         <v>2</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8921,7 +8978,7 @@
         <v>112</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>328</v>
@@ -8939,10 +8996,10 @@
         <v>2</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8950,7 +9007,7 @@
         <v>112</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>332</v>
@@ -8968,10 +9025,10 @@
         <v>2</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8979,7 +9036,7 @@
         <v>112</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>350</v>
@@ -8997,10 +9054,10 @@
         <v>3</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9008,7 +9065,7 @@
         <v>112</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>354</v>
@@ -9026,10 +9083,10 @@
         <v>3</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9037,28 +9094,28 @@
         <v>112</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G64" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9066,16 +9123,16 @@
         <v>112</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>15</v>
@@ -9084,10 +9141,10 @@
         <v>2</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9095,28 +9152,28 @@
         <v>112</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9124,28 +9181,28 @@
         <v>112</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>451</v>
+        <v>394</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>452</v>
+        <v>395</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>434</v>
+        <v>369</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9153,16 +9210,16 @@
         <v>112</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>543</v>
+        <v>456</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>545</v>
+        <v>457</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>544</v>
+        <v>439</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>15</v>
@@ -9171,10 +9228,10 @@
         <v>2</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9182,28 +9239,28 @@
         <v>112</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9211,28 +9268,28 @@
         <v>112</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>143</v>
+        <v>565</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>144</v>
+        <v>566</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>147</v>
+        <v>549</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9240,13 +9297,13 @@
         <v>112</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>127</v>
@@ -9255,13 +9312,13 @@
         <v>147</v>
       </c>
       <c r="G71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9269,13 +9326,13 @@
         <v>112</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>127</v>
@@ -9284,13 +9341,13 @@
         <v>147</v>
       </c>
       <c r="G72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9298,16 +9355,16 @@
         <v>112</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>398</v>
+        <v>152</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>399</v>
+        <v>153</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>364</v>
+        <v>127</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>147</v>
@@ -9316,10 +9373,10 @@
         <v>1</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9327,16 +9384,16 @@
         <v>112</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>147</v>
@@ -9345,10 +9402,10 @@
         <v>1</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="75" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9356,16 +9413,16 @@
         <v>112</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>147</v>
@@ -9374,10 +9431,10 @@
         <v>1</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="76" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9385,16 +9442,16 @@
         <v>112</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>147</v>
@@ -9403,10 +9460,10 @@
         <v>1</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9414,16 +9471,16 @@
         <v>112</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>478</v>
+        <v>439</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>147</v>
@@ -9432,10 +9489,10 @@
         <v>1</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="78" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9443,16 +9500,16 @@
         <v>112</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>147</v>
@@ -9461,10 +9518,10 @@
         <v>1</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="79" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9472,28 +9529,28 @@
         <v>112</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>107</v>
+        <v>495</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>108</v>
+        <v>496</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>111</v>
+        <v>483</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="80" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9501,16 +9558,16 @@
         <v>112</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>564</v>
+        <v>107</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>565</v>
+        <v>108</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>544</v>
+        <v>89</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>111</v>
@@ -9519,39 +9576,39 @@
         <v>1</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>272</v>
+        <v>569</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>274</v>
+        <v>570</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>14</v>
+        <v>549</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9559,13 +9616,13 @@
         <v>164</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>273</v>
@@ -9574,13 +9631,13 @@
         <v>14</v>
       </c>
       <c r="G82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9588,28 +9645,28 @@
         <v>164</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>15</v>
+      <c r="F83" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="G83" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9617,13 +9674,13 @@
         <v>164</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>273</v>
@@ -9635,10 +9692,10 @@
         <v>2</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="85" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9646,16 +9703,16 @@
         <v>164</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>15</v>
@@ -9664,10 +9721,10 @@
         <v>2</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="86" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9675,28 +9732,28 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>403</v>
+        <v>342</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9704,28 +9761,28 @@
         <v>164</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>498</v>
+        <v>407</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>500</v>
+        <v>408</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>499</v>
+        <v>369</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G87" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9733,16 +9790,16 @@
         <v>164</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>503</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>15</v>
@@ -9751,10 +9808,10 @@
         <v>2</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="89" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9762,7 +9819,7 @@
         <v>164</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>508</v>
@@ -9771,7 +9828,7 @@
         <v>509</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>15</v>
@@ -9780,10 +9837,10 @@
         <v>2</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="90" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9791,16 +9848,16 @@
         <v>164</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>557</v>
+        <v>514</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>544</v>
+        <v>504</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>15</v>
@@ -9809,10 +9866,10 @@
         <v>2</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9820,28 +9877,28 @@
         <v>164</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>226</v>
+        <v>561</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>227</v>
+        <v>562</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>147</v>
+        <v>549</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G91" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="92" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9849,16 +9906,16 @@
         <v>164</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>147</v>
@@ -9867,10 +9924,10 @@
         <v>1</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="93" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9878,13 +9935,13 @@
         <v>164</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>235</v>
@@ -9893,13 +9950,13 @@
         <v>147</v>
       </c>
       <c r="G93" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="94" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9907,28 +9964,28 @@
         <v>164</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>337</v>
+        <v>263</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>338</v>
+        <v>264</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G94" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="95" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9936,28 +9993,28 @@
         <v>164</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>512</v>
+        <v>337</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>513</v>
+        <v>338</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>499</v>
+        <v>304</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>147</v>
       </c>
       <c r="G95" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="96" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9965,16 +10022,16 @@
         <v>164</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>147</v>
@@ -9983,10 +10040,10 @@
         <v>1</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9994,16 +10051,16 @@
         <v>164</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>147</v>
@@ -10012,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10023,28 +10080,28 @@
         <v>164</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>160</v>
+        <v>553</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>161</v>
+        <v>554</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>111</v>
+        <v>549</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G98" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10052,28 +10109,28 @@
         <v>164</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10081,16 +10138,16 @@
         <v>164</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>111</v>
@@ -10099,10 +10156,10 @@
         <v>1</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10110,16 +10167,16 @@
         <v>164</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>111</v>
@@ -10128,10 +10185,10 @@
         <v>1</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10139,16 +10196,16 @@
         <v>164</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>429</v>
+        <v>251</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>430</v>
+        <v>252</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>409</v>
+        <v>235</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>111</v>
@@ -10157,10 +10214,10 @@
         <v>1</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10168,16 +10225,16 @@
         <v>164</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>495</v>
+        <v>435</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>478</v>
+        <v>414</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>111</v>
@@ -10186,10 +10243,10 @@
         <v>1</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10197,16 +10254,16 @@
         <v>164</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>111</v>
@@ -10215,39 +10272,39 @@
         <v>1</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>289</v>
+        <v>534</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>290</v>
+        <v>535</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>15</v>
+        <v>530</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G105" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10255,28 +10312,28 @@
         <v>271</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F106" s="9" t="s">
-        <v>147</v>
+      <c r="F106" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="G106" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10284,28 +10341,28 @@
         <v>271</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>111</v>
+        <v>273</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G107" s="2">
         <v>2</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10313,28 +10370,28 @@
         <v>271</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>516</v>
+        <v>267</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>517</v>
+        <v>268</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>499</v>
+        <v>235</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10342,16 +10399,16 @@
         <v>271</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>111</v>
@@ -10360,39 +10417,39 @@
         <v>1</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>147</v>
+        <v>504</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10400,28 +10457,28 @@
         <v>301</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>297</v>
+        <v>543</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>298</v>
+        <v>544</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>111</v>
+        <v>530</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="G111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10429,37 +10486,66 @@
         <v>301</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>533</v>
+        <v>297</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>534</v>
+        <v>298</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>525</v>
+        <v>273</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G112" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="H2:H112">
+    <dataValidation type="list" sqref="H2:H113">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I112">
+    <dataValidation type="list" sqref="I2:I113">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
